--- a/education_forms/040_educational_support_assessment--education_forms.xlsx
+++ b/education_forms/040_educational_support_assessment--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -931,8 +931,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -960,12 +960,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'academic_support'}</t>
+          <t>academic_support</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'academic_support'}</t>
+          <t>academic support</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'wellbeing_support'}</t>
+          <t>wellbeing_support</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'wellbeing_support'}</t>
+          <t>wellbeing support</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'tutor1'}</t>
+          <t>tutor1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Tutor1'}</t>
+          <t>Tutor1</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'tutor2'}</t>
+          <t>tutor2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Tutor2'}</t>
+          <t>Tutor2</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'tutor3'}</t>
+          <t>tutor3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Tutor3'}</t>
+          <t>Tutor3</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'counselor1'}</t>
+          <t>counselor1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Counselor1'}</t>
+          <t>Counselor1</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'counselor2'}</t>
+          <t>counselor2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Counselor2'}</t>
+          <t>Counselor2</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'counselor3'}</t>
+          <t>counselor3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Counselor3'}</t>
+          <t>Counselor3</t>
         </is>
       </c>
     </row>
